--- a/base/analise-financeira-cartesian.xlsx
+++ b/base/analise-financeira-cartesian.xlsx
@@ -21,9 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REGRESSAO_RSM2" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DISTRIBUICAO_MG'!$A$4:$I$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RSM2_POR_MG'!$A$3:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MO_MATERIAL'!$A$4:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DISTRIBUICAO_MG'!$A$4:$I$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RSM2_POR_MG'!$A$3:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MO_MATERIAL'!$A$4:$G$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CUSTO_INDIRETO'!$A$4:$D$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'QUARTIS_EFICIENCIA'!$A$4:$F$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'INSTALACOES'!$A$3:$H$10</definedName>
@@ -601,7 +601,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado 18/04/2026 00:59 . 126 projetos . 76 com total . 65 com rsm2</t>
+          <t>Gerado 18/04/2026 08:26 . 126 projetos . 76 com total . 65 com rsm2</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2012,29 +2012,29 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3.803</v>
+        <v>5.4768</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>6.9456</v>
+        <v>7.9265</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>13.6372</v>
+        <v>9.1028</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>19.7354</v>
+        <v>11.0984</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>22.222</v>
+        <v>18.9784</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>0.469</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="8">
@@ -2045,29 +2045,29 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>5.4768</v>
+        <v>0.6833</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>7.9265</v>
+        <v>7.0093</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>9.1028</v>
+        <v>8.855399999999999</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>11.0984</v>
+        <v>10.443</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>18.9784</v>
+        <v>13.0236</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.327</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="9">
@@ -2133,7 +2133,7 @@
         <v>13.7961</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>0.471</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="11">
@@ -2177,29 +2177,29 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1.6974</v>
+        <v>1.9313</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>4.4795</v>
+        <v>5.1155</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5.8562</v>
+        <v>5.8027</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>6.8039</v>
+        <v>6.4636</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>8.4742</v>
+        <v>8.5101</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>0.336</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="13">
@@ -2210,29 +2210,29 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1.9313</v>
+        <v>3.803</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5.1155</v>
+        <v>3.803</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5.8027</v>
+        <v>5.4201</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>6.4636</v>
+        <v>6.9456</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>8.5101</v>
+        <v>6.9456</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>0.236</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="14">
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.6833</v>
+        <v>1.0265</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>3.1763</v>
+        <v>3.2044</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4.6055</v>
+        <v>4.8734</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>6.357</v>
@@ -2265,7 +2265,7 @@
         <v>14.0412</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0.587</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="15">
@@ -2276,29 +2276,29 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Eletricas</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>3.2539</v>
+        <v>1.6974</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>3.8067</v>
+        <v>3.8431</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3.8472</v>
+        <v>4.8351</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>8.311400000000001</v>
+        <v>5.9832</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>10.9101</v>
+        <v>8.4742</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="16">
@@ -2309,29 +2309,29 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Pintura Interna</t>
+          <t>Instalacoes Eletricas</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1.9046</v>
+        <v>3.2539</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>2.2723</v>
+        <v>3.8067</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3.8457</v>
+        <v>3.8472</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.7073</v>
+        <v>8.311400000000001</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>5.4094</v>
+        <v>10.9101</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2394,10 +2394,10 @@
         <v>5.3002</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>12.337</v>
+        <v>9.276</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.629</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="19">
@@ -2408,29 +2408,29 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.9651999999999999</v>
+        <v>1.1029</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1.4796</v>
+        <v>3.191</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1.8828</v>
+        <v>3.6112</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>2.1436</v>
+        <v>5.4094</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>5.6301</v>
+        <v>5.8798</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0.501</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="20">
@@ -2441,29 +2441,29 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Pintura Interna</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.4295</v>
+        <v>1.9046</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1.2902</v>
+        <v>2.2723</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1.8344</v>
+        <v>3.2024</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>2.0555</v>
+        <v>4.7073</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>3.1482</v>
+        <v>5.2659</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.368</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="21">
@@ -2474,29 +2474,29 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.2132</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.2593</v>
+        <v>1.4796</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.9921</v>
+        <v>1.8828</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>1.0904</v>
+        <v>2.1436</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>5.2992</v>
+        <v>5.6301</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>1.352</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="22">
@@ -2507,29 +2507,29 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.457</v>
+        <v>0.4295</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.6999</v>
+        <v>1.2902</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.946</v>
+        <v>1.8344</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>1.4744</v>
+        <v>2.0555</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>4.8684</v>
+        <v>3.1482</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.927</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="23">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Loucas e Metais</t>
+          <t>Climatizacao</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.3966</v>
+        <v>0.457</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.4991</v>
+        <v>0.6999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.7776</v>
+        <v>1.1416</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>1.0514</v>
+        <v>2.9764</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>4.2947</v>
+        <v>4.8684</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>1.026</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="24">
@@ -2573,29 +2573,29 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Instalacoes Preventivas</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.1536</v>
+        <v>0.2132</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.2969</v>
+        <v>0.2593</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.6954</v>
+        <v>0.9921</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>1.0972</v>
+        <v>1.0904</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>2.2289</v>
+        <v>5.2992</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.706</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="25">
@@ -2606,95 +2606,95 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Loucas e Metais</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.1827</v>
+        <v>0.3966</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.3767</v>
+        <v>0.4991</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.4331</v>
+        <v>0.7776</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.4902</v>
+        <v>1.0514</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.6699000000000001</v>
+        <v>4.2947</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.411</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>5.9526</v>
+        <v>0.1536</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>15.4511</v>
+        <v>0.2969</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>19.4928</v>
+        <v>0.6954</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>22.8174</v>
+        <v>1.0972</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>41.3367</v>
+        <v>2.2289</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0.324</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>3.7346</v>
+        <v>0.1827</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>14.4506</v>
+        <v>0.3767</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>17.6548</v>
+        <v>0.4331</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>18.8941</v>
+        <v>0.4902</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>24.6464</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0.33</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="28">
@@ -2705,29 +2705,29 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>6.3848</v>
+        <v>5.9526</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>10.7708</v>
+        <v>15.4511</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>13.5548</v>
+        <v>19.4928</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>20.6468</v>
+        <v>22.8174</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>64.0303</v>
+        <v>41.3367</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.699</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="29">
@@ -2738,29 +2738,29 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1.579</v>
+        <v>6.3848</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>7.6621</v>
+        <v>10.7708</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>9.8843</v>
+        <v>13.5548</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>12.3573</v>
+        <v>20.6468</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>28.4523</v>
+        <v>64.0303</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0.526</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="30">
@@ -2771,29 +2771,29 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>3.7526</v>
+        <v>1.579</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>7.266</v>
+        <v>7.6621</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8.5649</v>
+        <v>9.8843</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>10.045</v>
+        <v>12.3573</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>16.62</v>
+        <v>28.4523</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.285</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="31">
@@ -2804,29 +2804,29 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1.6062</v>
+        <v>0.6606</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>5.101</v>
+        <v>7.6546</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7.9421</v>
+        <v>9.4726</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>10.2958</v>
+        <v>11.26</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>26.2811</v>
+        <v>23.8318</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0.555</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="32">
@@ -2837,29 +2837,29 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2.4115</v>
+        <v>3.7526</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>5.0691</v>
+        <v>7.266</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6.2336</v>
+        <v>8.5649</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>7.5704</v>
+        <v>10.045</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>24.395</v>
+        <v>16.62</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.556</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="33">
@@ -2870,29 +2870,29 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>2.5326</v>
+        <v>1.6062</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>4.0116</v>
+        <v>5.101</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5.4207</v>
+        <v>7.9421</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>7.5216</v>
+        <v>10.2958</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>22.3765</v>
+        <v>26.2811</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0.632</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="34">
@@ -2903,29 +2903,29 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1.3814</v>
+        <v>2.4115</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>1.4157</v>
+        <v>5.0691</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5.2065</v>
+        <v>6.2336</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>7.012</v>
+        <v>7.5704</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>7.9776</v>
+        <v>24.395</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0.631</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="35">
@@ -2936,29 +2936,29 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1.3877</v>
+        <v>2.5326</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>3.7774</v>
+        <v>4.0116</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5.0079</v>
+        <v>5.4207</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>6.2638</v>
+        <v>7.5216</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>10.9165</v>
+        <v>22.3765</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0.389</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="36">
@@ -2969,29 +2969,29 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1.5798</v>
+        <v>3.7346</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>3.4668</v>
+        <v>3.7346</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4.3434</v>
+        <v>5.0667</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>4.9586</v>
+        <v>10.2744</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>9.926299999999999</v>
+        <v>10.2744</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.393</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="37">
@@ -3002,29 +3002,29 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Eletricas</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>2.2704</v>
+        <v>1.3877</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>2.2704</v>
+        <v>3.5665</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4.2905</v>
+        <v>5.0079</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>6.5933</v>
+        <v>6.2638</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>6.5933</v>
+        <v>10.9165</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.493</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="38">
@@ -3035,29 +3035,29 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Pintura Interna</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1.2201</v>
+        <v>1.3814</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>3.3672</v>
+        <v>3.4452</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3.9382</v>
+        <v>4.4936</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>4.5512</v>
+        <v>6.0184</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>5.4178</v>
+        <v>8.6998</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.289</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="39">
@@ -3068,29 +3068,29 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.0893</v>
+        <v>1.5798</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>3.1554</v>
+        <v>3.4668</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3.6121</v>
+        <v>4.3434</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>4.5282</v>
+        <v>4.9586</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>10.7552</v>
+        <v>9.926299999999999</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0.465</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="40">
@@ -3101,29 +3101,29 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Instalacoes Eletricas</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.5644</v>
+        <v>2.2704</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1.3595</v>
+        <v>2.2704</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1.8607</v>
+        <v>4.2905</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>2.2137</v>
+        <v>6.5933</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>3.5132</v>
+        <v>6.5933</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.351</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="41">
@@ -3134,29 +3134,29 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Pintura Interna</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.6061</v>
+        <v>1.2201</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1.301</v>
+        <v>3.3672</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1.5938</v>
+        <v>3.9382</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>2.1346</v>
+        <v>4.5512</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>2.8805</v>
+        <v>5.4178</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0.329</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="42">
@@ -3167,29 +3167,29 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.3988</v>
+        <v>0.0893</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.6475</v>
+        <v>3.1554</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.9304</v>
+        <v>3.6121</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>2.0691</v>
+        <v>4.5282</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>4.8802</v>
+        <v>10.7552</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0.881</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="43">
@@ -3200,29 +3200,29 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.2919</v>
+        <v>0.66</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.2919</v>
+        <v>2.6466</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.7772</v>
+        <v>3.1451</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.8827</v>
+        <v>4.0425</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.8827</v>
+        <v>5.029</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0.484</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="44">
@@ -3233,29 +3233,29 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Loucas e Metais</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.2632</v>
+        <v>0.5644</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.7398</v>
+        <v>1.3595</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.7711</v>
+        <v>1.8607</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.9809</v>
+        <v>2.2137</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>2.2326</v>
+        <v>3.5132</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0.554</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="45">
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.112</v>
+        <v>0.6061</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.287</v>
+        <v>1.301</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.537</v>
+        <v>1.5938</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>1.0804</v>
+        <v>2.1346</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>12.9615</v>
+        <v>2.8805</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>1.902</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="46">
@@ -3299,161 +3299,161 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Climatizacao</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.0211</v>
+        <v>0.3988</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3591</v>
+        <v>0.6475</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.4787</v>
+        <v>0.9304</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>0.5808</v>
+        <v>2.0691</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>1.3248</v>
+        <v>4.8802</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.63</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Instalacoes Preventivas</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>18.6864</v>
+        <v>0.2919</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>18.6864</v>
+        <v>0.2919</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>19.7171</v>
+        <v>0.7772</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>20.7479</v>
+        <v>0.8827</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>20.7479</v>
+        <v>0.8827</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0.074</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Loucas e Metais</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>18.8172</v>
+        <v>0.2632</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>18.8172</v>
+        <v>0.7398</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>18.9457</v>
+        <v>0.7711</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>19.0742</v>
+        <v>0.9809</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>19.0742</v>
+        <v>2.2326</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0.01</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>9.970000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>9.970000000000001</v>
+        <v>0.287</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>10.6186</v>
+        <v>0.537</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>11.2673</v>
+        <v>1.0804</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>11.2673</v>
+        <v>12.9615</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.902</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>7.4232</v>
+        <v>0.0211</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>7.4232</v>
+        <v>0.3591</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>9.1426</v>
+        <v>0.4787</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>10.8619</v>
+        <v>0.5808</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>10.8619</v>
+        <v>1.3248</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>0.266</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="51">
@@ -3464,29 +3464,29 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>8.5505</v>
+        <v>18.8172</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>8.5505</v>
+        <v>18.8172</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>8.841799999999999</v>
+        <v>18.9457</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>9.132999999999999</v>
+        <v>19.0742</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>9.132999999999999</v>
+        <v>19.0742</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>0.047</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="52">
@@ -3497,29 +3497,29 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>5.6243</v>
+        <v>8.453200000000001</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>5.6243</v>
+        <v>8.453200000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>7.1351</v>
+        <v>10.802</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>8.645899999999999</v>
+        <v>13.1507</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>8.645899999999999</v>
+        <v>13.1507</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0.299</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="53">
@@ -3530,29 +3530,29 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>4.7883</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>4.7883</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>6.13</v>
+        <v>10.6186</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>7.4717</v>
+        <v>11.2673</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>7.4717</v>
+        <v>11.2673</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0.31</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -3563,29 +3563,29 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>4.3667</v>
+        <v>7.4232</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>4.3667</v>
+        <v>7.4232</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5.1401</v>
+        <v>9.1426</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>5.9135</v>
+        <v>10.8619</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>5.9135</v>
+        <v>10.8619</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0.213</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="55">
@@ -3596,29 +3596,29 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1.5832</v>
+        <v>8.5505</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1.5832</v>
+        <v>8.5505</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>5.016</v>
+        <v>8.841799999999999</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>8.4488</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>8.4488</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>0.968</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="56">
@@ -3629,29 +3629,29 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>2.4149</v>
+        <v>5.6243</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>2.4149</v>
+        <v>5.6243</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4.2516</v>
+        <v>7.1351</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>6.0882</v>
+        <v>8.645899999999999</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>6.0882</v>
+        <v>8.645899999999999</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>0.611</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="57">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>1.9479</v>
+        <v>4.7883</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>1.9479</v>
+        <v>4.7883</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2.0126</v>
+        <v>6.13</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>2.0773</v>
+        <v>7.4717</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>2.0773</v>
+        <v>7.4717</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>0.045</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="58">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1.0813</v>
+        <v>5.5223</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1.0813</v>
+        <v>5.5223</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1.8284</v>
+        <v>5.6108</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>2.5755</v>
+        <v>5.6993</v>
       </c>
       <c r="H58" s="11" t="n">
-        <v>2.5755</v>
+        <v>5.6993</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0.578</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="59">
@@ -3728,227 +3728,227 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>0.1898</v>
+        <v>4.3667</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.1898</v>
+        <v>4.3667</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1.2204</v>
+        <v>5.1401</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>2.2511</v>
+        <v>5.9135</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>2.2511</v>
+        <v>5.9135</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>1.194</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>17.6764</v>
+        <v>1.5832</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>17.6764</v>
+        <v>1.5832</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>19.8967</v>
+        <v>5.016</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>22.1169</v>
+        <v>8.4488</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>22.1169</v>
+        <v>8.4488</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>0.158</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>7.352</v>
+        <v>2.4149</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>7.352</v>
+        <v>2.4149</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>12.2483</v>
+        <v>4.2516</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>12.7889</v>
+        <v>6.0882</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>12.7889</v>
+        <v>6.0882</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>0.277</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>11.027</v>
+        <v>2.0749</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>11.027</v>
+        <v>2.0749</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>11.2857</v>
+        <v>3.3044</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>11.5445</v>
+        <v>4.5339</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>11.5445</v>
+        <v>4.5339</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>0.032</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>10.5261</v>
+        <v>1.9479</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>10.5261</v>
+        <v>1.9479</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>10.7242</v>
+        <v>2.0126</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>10.9223</v>
+        <v>2.0773</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>10.9223</v>
+        <v>2.0773</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>0.026</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>6.8221</v>
+        <v>1.0813</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>6.8221</v>
+        <v>1.0813</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>9.318899999999999</v>
+        <v>1.8284</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>13.1259</v>
+        <v>2.5755</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>13.1259</v>
+        <v>2.5755</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0.325</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>0.1898</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>0.1898</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>1.2204</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>2.2511</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>2.2511</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0</v>
+        <v>1.194</v>
       </c>
     </row>
     <row r="66">
@@ -3959,29 +3959,29 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>2.0658</v>
+        <v>17.6764</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>2.0658</v>
+        <v>17.6764</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>8.427300000000001</v>
+        <v>19.8967</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>16.4341</v>
+        <v>22.1169</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>16.4341</v>
+        <v>22.1169</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0.802</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="67">
@@ -3992,29 +3992,29 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Eletricas</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>8.1578</v>
+        <v>7.352</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>8.1578</v>
+        <v>7.352</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>8.1578</v>
+        <v>12.2483</v>
       </c>
       <c r="G67" s="11" t="n">
-        <v>8.1578</v>
+        <v>12.7889</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>8.1578</v>
+        <v>12.7889</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="68">
@@ -4025,29 +4025,29 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>3.83</v>
+        <v>11.027</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>3.83</v>
+        <v>11.027</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>7.9623</v>
+        <v>11.2857</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>9.082700000000001</v>
+        <v>11.5445</v>
       </c>
       <c r="H68" s="11" t="n">
-        <v>9.082700000000001</v>
+        <v>11.5445</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>0.398</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="69">
@@ -4058,29 +4058,29 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>6.2491</v>
+        <v>10.5261</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>6.2491</v>
+        <v>10.5261</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>6.2491</v>
+        <v>10.7242</v>
       </c>
       <c r="G69" s="11" t="n">
-        <v>6.2491</v>
+        <v>10.9223</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>6.2491</v>
+        <v>10.9223</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="70">
@@ -4091,29 +4091,29 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>4.8367</v>
+        <v>6.8221</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>4.8367</v>
+        <v>6.8221</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>5.9246</v>
+        <v>9.318899999999999</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>6.8195</v>
+        <v>13.1259</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>6.8195</v>
+        <v>13.1259</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0.169</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="71">
@@ -4124,29 +4124,29 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>5.4324</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>5.4324</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5.6171</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G71" s="11" t="n">
-        <v>5.6282</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>5.6282</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4157,29 +4157,29 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>4.0586</v>
+        <v>2.0658</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>4.0586</v>
+        <v>2.0658</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>4.4082</v>
+        <v>8.427300000000001</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>7.6554</v>
+        <v>16.4341</v>
       </c>
       <c r="H72" s="11" t="n">
-        <v>7.6554</v>
+        <v>16.4341</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0.369</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="73">
@@ -4190,29 +4190,29 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Pintura Interna</t>
+          <t>Instalacoes Eletricas</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>3.5083</v>
+        <v>8.1578</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.5083</v>
+        <v>8.1578</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3.8785</v>
+        <v>8.1578</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>3.9764</v>
+        <v>8.1578</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>3.9764</v>
+        <v>8.1578</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4223,29 +4223,29 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>3.5328</v>
+        <v>3.83</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>3.5328</v>
+        <v>3.83</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3.5328</v>
+        <v>7.9623</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>3.5328</v>
+        <v>9.082700000000001</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>3.5328</v>
+        <v>9.082700000000001</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="75">
@@ -4256,26 +4256,26 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>3.5306</v>
+        <v>6.2491</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>3.5306</v>
+        <v>6.2491</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3.5306</v>
+        <v>6.2491</v>
       </c>
       <c r="G75" s="11" t="n">
-        <v>3.5306</v>
+        <v>6.2491</v>
       </c>
       <c r="H75" s="11" t="n">
-        <v>3.5306</v>
+        <v>6.2491</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>0</v>
@@ -4289,29 +4289,29 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1.2925</v>
+        <v>4.8367</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.2925</v>
+        <v>4.8367</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2.7324</v>
+        <v>5.9246</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>4.1857</v>
+        <v>6.8195</v>
       </c>
       <c r="H76" s="11" t="n">
-        <v>4.1857</v>
+        <v>6.8195</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0.529</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="77">
@@ -4322,29 +4322,29 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>0.8385</v>
+        <v>5.4324</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>0.8385</v>
+        <v>5.4324</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1.9314</v>
+        <v>5.6171</v>
       </c>
       <c r="G77" s="11" t="n">
-        <v>2.102</v>
+        <v>5.6282</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>2.102</v>
+        <v>5.6282</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>0.422</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="78">
@@ -4355,29 +4355,29 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>0.5072</v>
+        <v>3.8251</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>0.5072</v>
+        <v>3.8251</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>0.6081</v>
+        <v>4.0586</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>0.7091</v>
+        <v>4.4082</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0.7091</v>
+        <v>4.4082</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>0.235</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -4388,59 +4388,59 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Pintura Interna</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>0.202</v>
+        <v>3.5083</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.202</v>
+        <v>3.5083</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.2877</v>
+        <v>3.8785</v>
       </c>
       <c r="G79" s="11" t="n">
-        <v>0.3734</v>
+        <v>3.9764</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>0.3734</v>
+        <v>3.9764</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>0.421</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>23.2038</v>
+        <v>3.8303</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>23.2038</v>
+        <v>3.8303</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>23.2038</v>
+        <v>3.8303</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>23.2038</v>
+        <v>3.8303</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>23.2038</v>
+        <v>3.8303</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>0</v>
@@ -4449,31 +4449,31 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Instalacoes Preventivas</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>14.0397</v>
+        <v>3.5328</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>14.0397</v>
+        <v>3.5328</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>14.0397</v>
+        <v>3.5328</v>
       </c>
       <c r="G81" s="11" t="n">
-        <v>14.0397</v>
+        <v>3.5328</v>
       </c>
       <c r="H81" s="11" t="n">
-        <v>14.0397</v>
+        <v>3.5328</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0</v>
@@ -4482,31 +4482,31 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Climatizacao</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>9.2768</v>
+        <v>3.5306</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>9.2768</v>
+        <v>3.5306</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>9.2768</v>
+        <v>3.5306</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>9.2768</v>
+        <v>3.5306</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>9.2768</v>
+        <v>3.5306</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>0</v>
@@ -4515,133 +4515,133 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>9.160500000000001</v>
+        <v>1.2925</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>9.160500000000001</v>
+        <v>1.2925</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>9.160500000000001</v>
+        <v>2.7324</v>
       </c>
       <c r="G83" s="11" t="n">
-        <v>9.160500000000001</v>
+        <v>4.1857</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>9.160500000000001</v>
+        <v>4.1857</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>8.394399999999999</v>
+        <v>0.8385</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>8.394399999999999</v>
+        <v>0.8385</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>8.394399999999999</v>
+        <v>1.9314</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>8.394399999999999</v>
+        <v>2.102</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>8.394399999999999</v>
+        <v>2.102</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>5.709</v>
+        <v>0.5072</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>5.709</v>
+        <v>0.5072</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>5.709</v>
+        <v>0.6081</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>5.709</v>
+        <v>0.7091</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>5.709</v>
+        <v>0.7091</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>5.6797</v>
+        <v>0.202</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>5.6797</v>
+        <v>0.202</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>5.6797</v>
+        <v>0.2877</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>5.6797</v>
+        <v>0.3734</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>5.6797</v>
+        <v>0.3734</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="87">
@@ -4652,26 +4652,26 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>5.3412</v>
+        <v>23.2038</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>5.3412</v>
+        <v>23.2038</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>5.3412</v>
+        <v>23.2038</v>
       </c>
       <c r="G87" s="11" t="n">
-        <v>5.3412</v>
+        <v>23.2038</v>
       </c>
       <c r="H87" s="11" t="n">
-        <v>5.3412</v>
+        <v>23.2038</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>0</v>
@@ -4685,26 +4685,26 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>5.0067</v>
+        <v>10.3051</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>5.0067</v>
+        <v>10.3051</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>5.0067</v>
+        <v>10.3051</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>5.0067</v>
+        <v>10.3051</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>5.0067</v>
+        <v>10.3051</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>
@@ -4718,26 +4718,26 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>4.8188</v>
+        <v>9.2768</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>4.8188</v>
+        <v>9.2768</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>4.8188</v>
+        <v>9.2768</v>
       </c>
       <c r="G89" s="11" t="n">
-        <v>4.8188</v>
+        <v>9.2768</v>
       </c>
       <c r="H89" s="11" t="n">
-        <v>4.8188</v>
+        <v>9.2768</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>
@@ -4751,26 +4751,26 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>3.94</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>3.94</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>3.94</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>3.94</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>3.94</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="I90" s="12" t="n">
         <v>0</v>
@@ -4784,26 +4784,26 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>2.0688</v>
+        <v>8.394399999999999</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>2.0688</v>
+        <v>8.394399999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2.0688</v>
+        <v>8.394399999999999</v>
       </c>
       <c r="G91" s="11" t="n">
-        <v>2.0688</v>
+        <v>8.394399999999999</v>
       </c>
       <c r="H91" s="11" t="n">
-        <v>2.0688</v>
+        <v>8.394399999999999</v>
       </c>
       <c r="I91" s="12" t="n">
         <v>0</v>
@@ -4817,26 +4817,26 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1.7014</v>
+        <v>5.709</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1.7014</v>
+        <v>5.709</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1.7014</v>
+        <v>5.709</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>1.7014</v>
+        <v>5.709</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>1.7014</v>
+        <v>5.709</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>0</v>
@@ -4850,33 +4850,297 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>1.6591</v>
+        <v>5.6797</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>1.6591</v>
+        <v>5.6797</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1.6591</v>
+        <v>5.6797</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>1.6591</v>
+        <v>5.6797</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>1.6591</v>
+        <v>5.6797</v>
       </c>
       <c r="I93" s="12" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Servicos Complementares</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>5.3412</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>5.3412</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>5.3412</v>
+      </c>
+      <c r="G94" s="11" t="n">
+        <v>5.3412</v>
+      </c>
+      <c r="H94" s="11" t="n">
+        <v>5.3412</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Pisos e Pavimentacoes</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>5.0067</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>5.0067</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>5.0067</v>
+      </c>
+      <c r="G95" s="11" t="n">
+        <v>5.0067</v>
+      </c>
+      <c r="H95" s="11" t="n">
+        <v>5.0067</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Revestimentos Parede</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>4.8188</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>4.8188</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>4.8188</v>
+      </c>
+      <c r="G96" s="11" t="n">
+        <v>4.8188</v>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>4.8188</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Alvenaria</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="G97" s="11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H97" s="11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Pintura Geral</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>3.7345</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>3.7345</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>3.7345</v>
+      </c>
+      <c r="G98" s="11" t="n">
+        <v>3.7345</v>
+      </c>
+      <c r="H98" s="11" t="n">
+        <v>3.7345</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Impermeabilizacao</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>2.0688</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>2.0688</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>2.0688</v>
+      </c>
+      <c r="G99" s="11" t="n">
+        <v>2.0688</v>
+      </c>
+      <c r="H99" s="11" t="n">
+        <v>2.0688</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Revestimentos Teto</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>1.7014</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>1.7014</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>1.7014</v>
+      </c>
+      <c r="G100" s="11" t="n">
+        <v>1.7014</v>
+      </c>
+      <c r="H100" s="11" t="n">
+        <v>1.7014</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Climatizacao</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="G101" s="11" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="H101" s="11" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I93"/>
+  <autoFilter ref="A4:I101"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -4892,7 +5156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5001,29 +5265,29 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>215.3236</v>
+        <v>240.0998</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>513.7465</v>
+        <v>507.7761</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>613.5117</v>
+        <v>558.7405</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>731.2614</v>
+        <v>942.6145</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>912.7609</v>
+        <v>2763.6024</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>0.317</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5034,29 +5298,29 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
         <v>18</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>240.0998</v>
+        <v>241.8392</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>507.7761</v>
+        <v>285.8608</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>558.7405</v>
+        <v>377.9766</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>942.6145</v>
+        <v>485.3473</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>2763.6024</v>
+        <v>990.5694999999999</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="7">
@@ -5067,29 +5331,29 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>138.8732</v>
+        <v>39.5373</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>248.0973</v>
+        <v>309.8792</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>414.4325</v>
+        <v>343.6912</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>425.613</v>
+        <v>428.57</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>444.6159</v>
+        <v>474.2213</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>0.403</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="8">
@@ -5100,29 +5364,29 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
         <v>18</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>241.8392</v>
+        <v>81.2659</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>285.8608</v>
+        <v>146.9058</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>377.9766</v>
+        <v>287.5181</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>485.3473</v>
+        <v>334.6088</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>990.5694999999999</v>
+        <v>599.4863</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.432</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="9">
@@ -5133,29 +5397,29 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>81.2659</v>
+        <v>60.535</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>153.1075</v>
+        <v>176.1791</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>287.5181</v>
+        <v>230.9255</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>334.6088</v>
+        <v>274.8992</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>599.4863</v>
+        <v>323.9574</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>0.525</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="10">
@@ -5166,29 +5430,29 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>60.535</v>
+        <v>156.4673</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>176.1791</v>
+        <v>187.4382</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>230.9255</v>
+        <v>222.3311</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>274.8992</v>
+        <v>365.2183</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>323.9574</v>
+        <v>638.2456</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>0.325</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="11">
@@ -5199,29 +5463,29 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>156.4673</v>
+        <v>215.3236</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>187.4382</v>
+        <v>215.3236</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>222.3311</v>
+        <v>215.3236</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>365.2183</v>
+        <v>215.3236</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>638.2456</v>
+        <v>215.3236</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5298,29 +5562,29 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>124.5631</v>
+        <v>85.5108</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>168</v>
+        <v>128.355</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>182.6851</v>
+        <v>192.5239</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>320.1339</v>
+        <v>248.0973</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>459.8208</v>
+        <v>444.6159</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0.516</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="15">
@@ -5331,29 +5595,29 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>55.9554</v>
+        <v>124.5631</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>125.3175</v>
+        <v>168</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>176.4962</v>
+        <v>182.6851</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>219.7913</v>
+        <v>320.1339</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>401.173</v>
+        <v>459.8208</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0.469</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="16">
@@ -5364,29 +5628,29 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>25.7107</v>
+        <v>55.9554</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>84.4721</v>
+        <v>125.3175</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>149.4185</v>
+        <v>176.4962</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>196.3616</v>
+        <v>219.7913</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>322.6675</v>
+        <v>401.173</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.527</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="17">
@@ -5397,29 +5661,29 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Pintura Interna</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>87.2655</v>
+        <v>88.5517</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>124.8759</v>
+        <v>114.0537</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>147.7893</v>
+        <v>159.1596</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>167.6997</v>
+        <v>179.3405</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>178.1544</v>
+        <v>252.1335</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0.22</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="18">
@@ -5430,29 +5694,29 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>26.3007</v>
+        <v>25.7107</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>54.1317</v>
+        <v>84.4721</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>64.6056</v>
+        <v>149.4185</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>85.02670000000001</v>
+        <v>196.3616</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>118.7749</v>
+        <v>322.6675</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.351</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="19">
@@ -5463,29 +5727,29 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Pintura Interna</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>38.729</v>
+        <v>87.2655</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>56.7906</v>
+        <v>124.8759</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>64.2199</v>
+        <v>136.3852</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>94.8934</v>
+        <v>176.2359</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>128.0419</v>
+        <v>178.1544</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0.378</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="20">
@@ -5496,29 +5760,29 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>24.2557</v>
+        <v>26.3007</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>28.2405</v>
+        <v>54.1317</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>40.062</v>
+        <v>64.6056</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>81.4457</v>
+        <v>85.02670000000001</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>124.6417</v>
+        <v>118.7749</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.643</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="21">
@@ -5529,29 +5793,29 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>13.0566</v>
+        <v>38.729</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>13.6029</v>
+        <v>56.7906</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>33.8035</v>
+        <v>64.2199</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>41.5472</v>
+        <v>94.8934</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>85</v>
+        <v>128.0419</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0.786</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="22">
@@ -5562,29 +5826,29 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Climatizacao</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>3.773</v>
+        <v>24.2557</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>11.4089</v>
+        <v>27.9799</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>30.7496</v>
+        <v>43.9189</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>68.81270000000001</v>
+        <v>81.4457</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>93.3381</v>
+        <v>124.6417</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.775</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="23">
@@ -5595,29 +5859,29 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Loucas e Metais</t>
+          <t>Instalacoes Preventivas</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>22.4522</v>
+        <v>13.0566</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>22.9323</v>
+        <v>13.6029</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>25.2351</v>
+        <v>33.8035</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>28.6773</v>
+        <v>41.5472</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>47.4129</v>
+        <v>85</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.33</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="24">
@@ -5628,95 +5892,95 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>7.9396</v>
+        <v>3.773</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>7.9396</v>
+        <v>11.4089</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>14.0251</v>
+        <v>30.7496</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>25.3516</v>
+        <v>68.81270000000001</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>25.3516</v>
+        <v>93.3381</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.475</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Loucas e Metais</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>310.0162</v>
+        <v>22.4522</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>456.4608</v>
+        <v>22.9323</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>650.1123</v>
+        <v>25.2351</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>700.688</v>
+        <v>28.6773</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>863.5048</v>
+        <v>47.4129</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.249</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>366.7062</v>
+        <v>7.9396</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>523.6348</v>
+        <v>7.9396</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>581.6932</v>
+        <v>14.0251</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>681.4036</v>
+        <v>25.3516</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>813.7787</v>
+        <v>25.3516</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0.205</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="27">
@@ -5727,29 +5991,29 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
         <v>31</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>60.7294</v>
+        <v>310.0162</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>336.4023</v>
+        <v>456.4608</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>462.5974</v>
+        <v>650.1123</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>940.3581</v>
+        <v>700.688</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>4909.9688</v>
+        <v>863.5048</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>1.286</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="28">
@@ -5760,29 +6024,29 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>113.0526</v>
+        <v>60.7294</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>159.2638</v>
+        <v>336.4023</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>310.2418</v>
+        <v>462.5974</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>388.3663</v>
+        <v>940.3581</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>464.1146</v>
+        <v>4909.9688</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.42</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="29">
@@ -5793,29 +6057,29 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>200.8093</v>
+        <v>22.3164</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>256.9109</v>
+        <v>284.5803</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>298.1404</v>
+        <v>317.1925</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>344.2307</v>
+        <v>389.8314</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>547.8138</v>
+        <v>597.665</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0.28</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="30">
@@ -5826,29 +6090,29 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>74.1056</v>
+        <v>113.0526</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>152.5097</v>
+        <v>159.2638</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>215.422</v>
+        <v>310.2418</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>287.6206</v>
+        <v>388.3663</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>1063.1919</v>
+        <v>464.1146</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.723</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="31">
@@ -5859,29 +6123,29 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>94.1782</v>
+        <v>200.8093</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>153.3493</v>
+        <v>256.9109</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>214.6932</v>
+        <v>298.1404</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>268.9397</v>
+        <v>344.2307</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>587.7851000000001</v>
+        <v>547.8138</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0.462</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="32">
@@ -5892,29 +6156,29 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Eletricas</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>162.5526</v>
+        <v>74.1056</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>162.5526</v>
+        <v>152.5097</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>195.2022</v>
+        <v>215.422</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>227.8518</v>
+        <v>287.6206</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>227.8518</v>
+        <v>1063.1919</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.237</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="33">
@@ -5925,29 +6189,29 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>47.8274</v>
+        <v>94.1782</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>47.8274</v>
+        <v>153.3493</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>192.8633</v>
+        <v>214.6932</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>289.4794</v>
+        <v>268.9397</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>289.4794</v>
+        <v>587.7851000000001</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0.588</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="34">
@@ -5958,29 +6222,29 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Instalacoes Eletricas</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>49.6431</v>
+        <v>162.5526</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>141.5484</v>
+        <v>162.5526</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>184.4638</v>
+        <v>195.2022</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>233.6945</v>
+        <v>227.8518</v>
       </c>
       <c r="H34" s="14" t="n">
-        <v>835.1315</v>
+        <v>227.8518</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="35">
@@ -5991,29 +6255,29 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>92.2747</v>
+        <v>49.6431</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>122.3812</v>
+        <v>141.5484</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>160.0401</v>
+        <v>184.4638</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>193.6116</v>
+        <v>233.6945</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>276.1129</v>
+        <v>835.1315</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0.308</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -6024,29 +6288,29 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
         <v>30</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>47.1963</v>
+        <v>92.2747</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>113.3533</v>
+        <v>122.2913</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>131.6456</v>
+        <v>160.0401</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>157.3138</v>
+        <v>193.6116</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>320.4948</v>
+        <v>276.1129</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.445</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="37">
@@ -6057,29 +6321,29 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Pintura Interna</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>44.5372</v>
+        <v>47.8274</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>114.5202</v>
+        <v>114.6167</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>128.0244</v>
+        <v>151.2293</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>153.4743</v>
+        <v>203.9426</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>196.8042</v>
+        <v>314.4358</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.305</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="38">
@@ -6090,29 +6354,29 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>6.8456</v>
+        <v>47.1963</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>93.80159999999999</v>
+        <v>113.3533</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>117.767</v>
+        <v>131.6456</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>166.1889</v>
+        <v>157.3138</v>
       </c>
       <c r="H38" s="14" t="n">
-        <v>300.4729</v>
+        <v>320.4948</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.506</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="39">
@@ -6123,29 +6387,29 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Pintura Interna</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>33.249</v>
+        <v>44.5372</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>43.2773</v>
+        <v>114.5202</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>56.8058</v>
+        <v>128.0244</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>68.7881</v>
+        <v>153.4743</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>120.9691</v>
+        <v>196.8042</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0.355</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="40">
@@ -6156,29 +6420,29 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>16.7192</v>
+        <v>6.8456</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>41.1731</v>
+        <v>93.80159999999999</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>55.2809</v>
+        <v>117.767</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>65.4143</v>
+        <v>166.1889</v>
       </c>
       <c r="H40" s="14" t="n">
-        <v>101.9305</v>
+        <v>300.4729</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.389</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="41">
@@ -6189,29 +6453,29 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>21.1896</v>
+        <v>39.4576</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>29.3728</v>
+        <v>88.3413</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>30.595</v>
+        <v>116.026</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>68.1981</v>
+        <v>135.0167</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>212.6921</v>
+        <v>149.5874</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>1.013</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="42">
@@ -6222,29 +6486,29 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Loucas e Metais</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>20.1789</v>
+        <v>33.249</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>24.7943</v>
+        <v>43.2773</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>30.4552</v>
+        <v>56.8058</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>37.9619</v>
+        <v>68.7881</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>82.4164</v>
+        <v>120.9691</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="43">
@@ -6255,29 +6519,29 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>20.9</v>
+        <v>16.7192</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>20.9</v>
+        <v>41.1731</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>23.88</v>
+        <v>55.2809</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>26.86</v>
+        <v>65.4143</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>26.86</v>
+        <v>101.9305</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0.176</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="44">
@@ -6288,29 +6552,29 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Climatizacao</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>4.7466</v>
+        <v>21.1896</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>13.8487</v>
+        <v>29.3728</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>17.9024</v>
+        <v>30.595</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>33.8124</v>
+        <v>68.1981</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>49.1428</v>
+        <v>212.6921</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0.595</v>
+        <v>1.013</v>
       </c>
     </row>
     <row r="45">
@@ -6321,128 +6585,128 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Loucas e Metais</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>4.5</v>
+        <v>20.1789</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>13.1227</v>
+        <v>24.7943</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>17.8991</v>
+        <v>30.4552</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>40.0759</v>
+        <v>37.9619</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>141.6294</v>
+        <v>82.4164</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>1.092</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Instalacoes Preventivas</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>424.3694</v>
+        <v>20.9</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>424.3694</v>
+        <v>20.9</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>502.3509</v>
+        <v>23.88</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>580.3324</v>
+        <v>26.86</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>580.3324</v>
+        <v>26.86</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.22</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>433.1773</v>
+        <v>4.7466</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>433.1773</v>
+        <v>13.8487</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>479.7533</v>
+        <v>17.9024</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>526.3293</v>
+        <v>33.8124</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>526.3293</v>
+        <v>49.1428</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0.137</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>255.8813</v>
+        <v>4.5</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>255.8813</v>
+        <v>13.1227</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>267.3741</v>
+        <v>17.8991</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>278.8668</v>
+        <v>40.0759</v>
       </c>
       <c r="H48" s="14" t="n">
-        <v>278.8668</v>
+        <v>141.6294</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0.061</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="49">
@@ -6453,29 +6717,29 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>168.5822</v>
+        <v>433.1773</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>168.5822</v>
+        <v>433.1773</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>236.1983</v>
+        <v>479.7533</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>303.8143</v>
+        <v>526.3293</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>303.8143</v>
+        <v>526.3293</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0.405</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="50">
@@ -6486,29 +6750,29 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>207.4122</v>
+        <v>191.9722</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>207.4122</v>
+        <v>191.9722</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>223.2875</v>
+        <v>279.9036</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>239.1628</v>
+        <v>367.835</v>
       </c>
       <c r="H50" s="14" t="n">
-        <v>239.1628</v>
+        <v>367.835</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>0.101</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="51">
@@ -6519,29 +6783,29 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>157.3154</v>
+        <v>255.8813</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>157.3154</v>
+        <v>255.8813</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>176.8322</v>
+        <v>267.3741</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>196.349</v>
+        <v>278.8668</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>196.349</v>
+        <v>278.8668</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>0.156</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="52">
@@ -6552,29 +6816,29 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>133.9315</v>
+        <v>168.5822</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>133.9315</v>
+        <v>168.5822</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>151.8074</v>
+        <v>236.1983</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>169.6833</v>
+        <v>303.8143</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>169.6833</v>
+        <v>303.8143</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0.167</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="53">
@@ -6585,29 +6849,29 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>35.9549</v>
+        <v>207.4122</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>35.9549</v>
+        <v>207.4122</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>136.1366</v>
+        <v>223.2875</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>236.3183</v>
+        <v>239.1628</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>236.3183</v>
+        <v>239.1628</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>1.041</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="54">
@@ -6618,29 +6882,29 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>122.1386</v>
+        <v>157.3154</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>122.1386</v>
+        <v>157.3154</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>128.2176</v>
+        <v>176.8322</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>134.2965</v>
+        <v>196.349</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>134.2965</v>
+        <v>196.349</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0.067</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="55">
@@ -6651,29 +6915,29 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>67.5476</v>
+        <v>133.9315</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>67.5476</v>
+        <v>133.9315</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>102.906</v>
+        <v>151.8074</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>138.2644</v>
+        <v>169.6833</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>138.2644</v>
+        <v>169.6833</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>0.486</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="56">
@@ -6684,29 +6948,29 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>44.2364</v>
+        <v>129.4314</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>44.2364</v>
+        <v>129.4314</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>51.17</v>
+        <v>141.9465</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>58.1035</v>
+        <v>154.4616</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>58.1035</v>
+        <v>154.4616</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>0.192</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="57">
@@ -6717,29 +6981,29 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>30.2442</v>
+        <v>35.9549</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>30.2442</v>
+        <v>35.9549</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>44.3675</v>
+        <v>136.1366</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>58.4907</v>
+        <v>236.3183</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>58.4907</v>
+        <v>236.3183</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>0.45</v>
+        <v>1.041</v>
       </c>
     </row>
     <row r="58">
@@ -6750,194 +7014,194 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>4.3107</v>
+        <v>122.1386</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>4.3107</v>
+        <v>122.1386</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>33.6372</v>
+        <v>128.2176</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>62.9637</v>
+        <v>134.2965</v>
       </c>
       <c r="H58" s="14" t="n">
-        <v>62.9637</v>
+        <v>134.2965</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>1.233</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>350.5882</v>
+        <v>67.5476</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>350.5882</v>
+        <v>67.5476</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>465.5562</v>
+        <v>102.906</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>580.5242</v>
+        <v>138.2644</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>580.5242</v>
+        <v>138.2644</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>0.349</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>228.969</v>
+        <v>58.0358</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>228.969</v>
+        <v>58.0358</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>259.2032</v>
+        <v>80.5008</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>289.4374</v>
+        <v>102.9658</v>
       </c>
       <c r="H60" s="14" t="n">
-        <v>289.4374</v>
+        <v>102.9658</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>0.165</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>208.7722</v>
+        <v>44.2364</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>208.7722</v>
+        <v>44.2364</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>247.7309</v>
+        <v>51.17</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>286.6896</v>
+        <v>58.1035</v>
       </c>
       <c r="H61" s="14" t="n">
-        <v>286.6896</v>
+        <v>58.1035</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>0.222</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>111.7217</v>
+        <v>30.2442</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>111.7217</v>
+        <v>30.2442</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>242.9295</v>
+        <v>44.3675</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>335.6825</v>
+        <v>58.4907</v>
       </c>
       <c r="H62" s="14" t="n">
-        <v>335.6825</v>
+        <v>58.4907</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>0.489</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>54.2243</v>
+        <v>4.3107</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>54.2243</v>
+        <v>4.3107</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>167.1443</v>
+        <v>33.6372</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>249.7327</v>
+        <v>62.9637</v>
       </c>
       <c r="H63" s="14" t="n">
-        <v>249.7327</v>
+        <v>62.9637</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>0.625</v>
+        <v>1.233</v>
       </c>
     </row>
     <row r="64">
@@ -6948,29 +7212,29 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" s="14" t="n">
-        <v>135.3074</v>
+        <v>350.5882</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>135.3074</v>
+        <v>350.5882</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>141.6101</v>
+        <v>465.5562</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>344.5297</v>
+        <v>580.5242</v>
       </c>
       <c r="H64" s="14" t="n">
-        <v>344.5297</v>
+        <v>580.5242</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0.575</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="65">
@@ -6981,29 +7245,29 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Parede</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>131.2932</v>
+        <v>228.969</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>131.2932</v>
+        <v>228.969</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>131.2932</v>
+        <v>259.2032</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>131.2932</v>
+        <v>289.4374</v>
       </c>
       <c r="H65" s="14" t="n">
-        <v>131.2932</v>
+        <v>289.4374</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="66">
@@ -7014,29 +7278,29 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="14" t="n">
-        <v>90.0304</v>
+        <v>208.7722</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>90.0304</v>
+        <v>208.7722</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>126.9525</v>
+        <v>247.7309</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>135.256</v>
+        <v>286.6896</v>
       </c>
       <c r="H66" s="14" t="n">
-        <v>135.256</v>
+        <v>286.6896</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0.205</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="67">
@@ -7047,29 +7311,29 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Eletricas</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" s="14" t="n">
-        <v>123.9662</v>
+        <v>111.7217</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>123.9662</v>
+        <v>111.7217</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>123.9662</v>
+        <v>242.9295</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>123.9662</v>
+        <v>335.6825</v>
       </c>
       <c r="H67" s="14" t="n">
-        <v>123.9662</v>
+        <v>335.6825</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="68">
@@ -7080,29 +7344,29 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D68" s="14" t="n">
-        <v>100.5291</v>
+        <v>54.2243</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>100.5291</v>
+        <v>54.2243</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>120.9949</v>
+        <v>167.1443</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>180.1426</v>
+        <v>249.7327</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>180.1426</v>
+        <v>249.7327</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>0.309</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="69">
@@ -7113,29 +7377,29 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>85.358</v>
+        <v>135.3074</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>85.358</v>
+        <v>135.3074</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>111.627</v>
+        <v>141.6101</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>142.5894</v>
+        <v>344.5297</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>142.5894</v>
+        <v>344.5297</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>0.253</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="70">
@@ -7146,29 +7410,29 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Revestimentos Parede</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>87.4316</v>
+        <v>131.2932</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>87.4316</v>
+        <v>131.2932</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>106.5299</v>
+        <v>131.2932</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>116.3324</v>
+        <v>131.2932</v>
       </c>
       <c r="H70" s="14" t="n">
-        <v>116.3324</v>
+        <v>131.2932</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0.142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -7179,29 +7443,29 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" s="14" t="n">
-        <v>94.96129999999999</v>
+        <v>90.0304</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>94.96129999999999</v>
+        <v>90.0304</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>94.96129999999999</v>
+        <v>126.9525</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>94.96129999999999</v>
+        <v>135.256</v>
       </c>
       <c r="H71" s="14" t="n">
-        <v>94.96129999999999</v>
+        <v>135.256</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="72">
@@ -7212,29 +7476,29 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Pintura Interna</t>
+          <t>Instalacoes Eletricas</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>53.3123</v>
+        <v>123.9662</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>53.3123</v>
+        <v>123.9662</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>78.86669999999999</v>
+        <v>123.9662</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>101.8022</v>
+        <v>123.9662</v>
       </c>
       <c r="H72" s="14" t="n">
-        <v>101.8022</v>
+        <v>123.9662</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0.311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -7245,29 +7509,29 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>25.636</v>
+        <v>100.5291</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>25.636</v>
+        <v>100.5291</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>63.6063</v>
+        <v>120.9949</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>71.72029999999999</v>
+        <v>180.1426</v>
       </c>
       <c r="H73" s="14" t="n">
-        <v>71.72029999999999</v>
+        <v>180.1426</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>0.459</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="74">
@@ -7278,29 +7542,29 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>53.6848</v>
+        <v>85.358</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>53.6848</v>
+        <v>85.358</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>53.6848</v>
+        <v>111.627</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>53.6848</v>
+        <v>142.5894</v>
       </c>
       <c r="H74" s="14" t="n">
-        <v>53.6848</v>
+        <v>142.5894</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="75">
@@ -7311,26 +7575,26 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>53.6507</v>
+        <v>94.96129999999999</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>53.6507</v>
+        <v>94.96129999999999</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>53.6507</v>
+        <v>94.96129999999999</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>53.6507</v>
+        <v>94.96129999999999</v>
       </c>
       <c r="H75" s="14" t="n">
-        <v>53.6507</v>
+        <v>94.96129999999999</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>0</v>
@@ -7344,29 +7608,29 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>16.6307</v>
+        <v>58.1271</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>16.6307</v>
+        <v>58.1271</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>29.3494</v>
+        <v>87.4316</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>55.174</v>
+        <v>106.5299</v>
       </c>
       <c r="H76" s="14" t="n">
-        <v>55.174</v>
+        <v>106.5299</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0.582</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="77">
@@ -7377,29 +7641,29 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Pintura Interna</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>10.0596</v>
+        <v>53.3123</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>10.0596</v>
+        <v>53.3123</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>14.336</v>
+        <v>78.86669999999999</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>18.6125</v>
+        <v>101.8022</v>
       </c>
       <c r="H77" s="14" t="n">
-        <v>18.6125</v>
+        <v>101.8022</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>0.422</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="78">
@@ -7410,33 +7674,231 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
+          <t>Revestimentos Teto</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>25.636</v>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>25.636</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>63.6063</v>
+      </c>
+      <c r="G78" s="14" t="n">
+        <v>71.72029999999999</v>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>71.72029999999999</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>0.459</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>economico</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Pintura Geral</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>58.2053</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>58.2053</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>58.2053</v>
+      </c>
+      <c r="G79" s="14" t="n">
+        <v>58.2053</v>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>58.2053</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>economico</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Instalacoes Preventivas</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>53.6848</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>53.6848</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>53.6848</v>
+      </c>
+      <c r="G80" s="14" t="n">
+        <v>53.6848</v>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>53.6848</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>economico</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Climatizacao</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>53.6507</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>53.6507</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>53.6507</v>
+      </c>
+      <c r="G81" s="14" t="n">
+        <v>53.6507</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>53.6507</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>economico</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Impermeabilizacao</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>16.6307</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>16.6307</v>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>29.3494</v>
+      </c>
+      <c r="G82" s="14" t="n">
+        <v>55.174</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>55.174</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>0.582</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>economico</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Movimentacao de Terra</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="14" t="n">
+        <v>10.0596</v>
+      </c>
+      <c r="E83" s="14" t="n">
+        <v>10.0596</v>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="G83" s="14" t="n">
+        <v>18.6125</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>18.6125</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>0.422</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>economico</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="C78" s="10" t="n">
+      <c r="C84" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D78" s="14" t="n">
+      <c r="D84" s="14" t="n">
         <v>4.0072</v>
       </c>
-      <c r="E78" s="14" t="n">
+      <c r="E84" s="14" t="n">
         <v>4.0072</v>
       </c>
-      <c r="F78" s="14" t="n">
+      <c r="F84" s="14" t="n">
         <v>6.9043</v>
       </c>
-      <c r="G78" s="14" t="n">
+      <c r="G84" s="14" t="n">
         <v>9.801299999999999</v>
       </c>
-      <c r="H78" s="14" t="n">
+      <c r="H84" s="14" t="n">
         <v>9.801299999999999</v>
       </c>
-      <c r="I78" s="12" t="n">
+      <c r="I84" s="12" t="n">
         <v>0.593</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I78"/>
+  <autoFilter ref="A3:I84"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -7451,7 +7913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7903,16 +8365,16 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>48.05</v>
+        <v>43.1</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>100</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>148.05</v>
+        <v>143.1</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -7928,20 +8390,20 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>7.4</v>
+        <v>58.85</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>93.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>101</v>
+        <v>151.25</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -7957,24 +8419,24 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>100</v>
+        <v>7.4</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -7986,24 +8448,24 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.8</v>
+        <v>100</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>100</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>100.8</v>
+        <v>200</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>COMPRA (material alto)</t>
+          <t>Misto</t>
         </is>
       </c>
     </row>
@@ -8015,20 +8477,20 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>15.6</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>97.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>113.25</v>
+        <v>100.8</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -8044,20 +8506,20 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Sistemas Especiais</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>28.85</v>
+        <v>15.6</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>85.8</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>114.65</v>
+        <v>113.25</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -8068,25 +8530,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Alvenaria</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>30.4</v>
+        <v>28.85</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>70.15000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>100.55</v>
+        <v>114.65</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -8102,24 +8564,24 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Climatizacao</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>74.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>100</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>174.6</v>
+        <v>100.55</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -8131,24 +8593,24 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Climatizacao</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>71.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>100</v>
+        <v>174.6</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>EMPREITADA (MO alta)</t>
+          <t>Misto</t>
         </is>
       </c>
     </row>
@@ -8160,24 +8622,24 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>1.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>99.05</v>
+        <v>28.6</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>100.15</v>
+        <v>100</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>COMPRA (material alto)</t>
+          <t>EMPREITADA (MO alta)</t>
         </is>
       </c>
     </row>
@@ -8189,24 +8651,24 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Fachada</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>78.7</v>
+        <v>1.1</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>21.3</v>
+        <v>99.05</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>100</v>
+        <v>100.15</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>EMPREITADA (MO alta)</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -8218,24 +8680,24 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Fachada</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>200</v>
-      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>EMPREITADA (MO alta)</t>
         </is>
       </c>
     </row>
@@ -8247,24 +8709,24 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Impermeabilizacao</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>39.65</v>
+        <v>100</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>87.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>127.25</v>
+        <v>200</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>COMPRA (material alto)</t>
+          <t>Misto</t>
         </is>
       </c>
     </row>
@@ -8276,20 +8738,20 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Impermeabilizacao</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>23.5</v>
+        <v>39.65</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>100</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>123.5</v>
+        <v>127.25</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
@@ -8305,20 +8767,20 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Eletricas</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>37.3</v>
+        <v>23.5</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>84.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>122.15</v>
+        <v>123.5</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -8334,24 +8796,24 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Instalacoes Eletricas</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>50</v>
+        <v>37.3</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>57.8</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>107.8</v>
+        <v>122.15</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -8363,20 +8825,20 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Preventivas</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>52.25</v>
+        <v>50</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>69</v>
+        <v>57.8</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>121.25</v>
+        <v>107.8</v>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
@@ -8392,24 +8854,24 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Loucas e Metais</t>
+          <t>Instalacoes Preventivas</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>19.7</v>
+        <v>52.25</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>119.7</v>
+        <v>121.25</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>COMPRA (material alto)</t>
+          <t>Misto</t>
         </is>
       </c>
     </row>
@@ -8421,22 +8883,24 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Movimentacao de Terra</t>
+          <t>Loucas e Metais</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="13" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>19.7</v>
+      </c>
       <c r="E36" s="13" t="n">
         <v>100</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>100</v>
+        <v>119.7</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -8448,24 +8912,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Movimentacao de Terra</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>55.1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D37" s="13" t="n"/>
       <c r="E37" s="13" t="n">
         <v>100</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>155.1</v>
+        <v>100</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>COMPRA (material alto)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8939,24 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="13" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>37.95</v>
+      </c>
       <c r="E38" s="13" t="n">
         <v>100</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>100</v>
+        <v>137.95</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -8504,24 +8968,24 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Revestimentos Teto</t>
+          <t>Pintura Geral</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>49.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>75.45</v>
+        <v>34.9</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>124.55</v>
+        <v>100</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>COMPRA (material alto)</t>
+          <t>EMPREITADA (MO alta)</t>
         </is>
       </c>
     </row>
@@ -8533,11 +8997,11 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D40" s="13" t="n"/>
       <c r="E40" s="13" t="n">
@@ -8560,22 +9024,24 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Sistemas Especiais</t>
+          <t>Revestimentos Teto</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="13" t="n"/>
+      <c r="D41" s="13" t="n">
+        <v>49.1</v>
+      </c>
       <c r="E41" s="13" t="n">
-        <v>100</v>
+        <v>75.45</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>100</v>
+        <v>124.55</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
@@ -8587,29 +9053,83 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="13" t="n">
-        <v>35</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D42" s="13" t="n"/>
       <c r="E42" s="13" t="n">
         <v>100</v>
       </c>
       <c r="F42" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Sistemas Especiais</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Supraestrutura</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="13" t="n">
         <v>135</v>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>COMPRA (material alto)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G42"/>
+  <autoFilter ref="A4:G44"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
